--- a/artfynd/A 53608-2025 artfynd.xlsx
+++ b/artfynd/A 53608-2025 artfynd.xlsx
@@ -1055,7 +1055,7 @@
         <v>136596610</v>
       </c>
       <c r="B5" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 53608-2025 artfynd.xlsx
+++ b/artfynd/A 53608-2025 artfynd.xlsx
@@ -1055,7 +1055,7 @@
         <v>136596610</v>
       </c>
       <c r="B5" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 53608-2025 artfynd.xlsx
+++ b/artfynd/A 53608-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1440,67 +1440,61 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110734138</v>
+        <v>137428300</v>
       </c>
       <c r="B8" t="n">
-        <v>8444</v>
+        <v>43487</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>100943</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>fönsterfälla</t>
-        </is>
-      </c>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Grundsjömossarnas NR  i väster, Upl</t>
+          <t>Hummelsvedjan, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>692036</v>
+        <v>691893</v>
       </c>
       <c r="R8" t="n">
-        <v>6661991</v>
+        <v>6661893</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1524,17 +1518,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-07-09</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>IBL2-fälla</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1543,28 +1532,879 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>blandskog invid häll, död stående björk</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>olvon</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Viburnum opulus</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>1 m upp</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Viburnum opulus # 1 m upp</t>
+        </is>
+      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137428300</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137428301</v>
+      </c>
+      <c r="B9" t="n">
+        <v>43487</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hummelsvedjan, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>691894</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6661894</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>olvon</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Viburnum opulus</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>1 m upp</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Viburnum opulus # 1 m upp</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137428301</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137428302</v>
+      </c>
+      <c r="B10" t="n">
+        <v>43487</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hummelsvedjan, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>691994</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6661962</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>olvon</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Viburnum opulus</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>1 m upp</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Viburnum opulus # 1 m upp</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137428302</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137428303</v>
+      </c>
+      <c r="B11" t="n">
+        <v>43487</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hummelsvedjan, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>691901</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6661902</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>olvon</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Viburnum opulus</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>1 m upp</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Viburnum opulus # 1 m upp</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137428303</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137428304</v>
+      </c>
+      <c r="B12" t="n">
+        <v>43487</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hummelsvedjan, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>691899</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6661904</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>olvon</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Viburnum opulus</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>1 m upp</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Viburnum opulus # 1 m upp</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137428304</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137428305</v>
+      </c>
+      <c r="B13" t="n">
+        <v>43487</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hummelsvedjan, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>691898</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6661903</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>olvon</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Viburnum opulus</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>1 m upp</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Viburnum opulus # 1 m upp</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137428305</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>110734138</v>
+      </c>
+      <c r="B14" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>fönsterfälla</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Grundsjömossarnas NR  i väster, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>692036</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6661991</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-06-12</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-07-09</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>IBL2-fälla</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>blandskog invid häll, död stående björk</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
           <t>Hans-Erik Wanntorp</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AX14" t="inlineStr">
         <is>
           <t>Hans-Erik Wanntorp, Kristoffer Stighäll</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
-      <c r="AZ8" t="inlineStr">
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/110734138</t>
         </is>
@@ -1579,6 +2419,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
